--- a/TestKit/HTTP_1/Environment.xlsx
+++ b/TestKit/HTTP_1/Environment.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\HTTP_PE_Contruct\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\School\NET\auto-grading\TestKit\HTTP_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5AD065-FB20-498A-AD89-973CCAE82BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5F0250-84E7-4D42-8848-1A6CA6A5F19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -50,9 +50,6 @@
     <t>Code_Image_Name</t>
   </si>
   <si>
-    <t>fptuxaes/aes-dotnet8:latest</t>
-  </si>
-  <si>
     <t>Code_Container_Name</t>
   </si>
   <si>
@@ -210,6 +207,9 @@
   </si>
   <si>
     <t>Meta\PE PRN222 sp25.sql</t>
+  </si>
+  <si>
+    <t>fptuxaes/aes-dotnet8-console:latest</t>
   </si>
 </sst>
 </file>
@@ -907,84 +907,84 @@
         <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="19">
-        <v>80</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="21">
-        <v>8081</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="10"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="11"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="12"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>18</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>20</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="13">
         <v>1433</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="13">
         <v>1434</v>
@@ -1000,53 +1000,53 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="14" t="s">
         <v>29</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="13"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="15"/>
     </row>
@@ -1070,98 +1070,98 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="27"/>
       <c r="B3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="27"/>
       <c r="B5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="27"/>
       <c r="B6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="27"/>
       <c r="B8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="27"/>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="27"/>
       <c r="B10" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="29"/>
       <c r="B11" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="4"/>
     </row>
@@ -1187,10 +1187,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>54</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1206,7 +1206,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1214,22 +1214,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
